--- a/input/industry/hotmaps_Info.xlsx
+++ b/input/industry/hotmaps_Info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Projekte\endemo\input\industry\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Projekte\endemo_Projects\endemo-ENS\endemo_IND_world_branch\endemo\input\industry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF75F39-810A-41BD-A0D0-F892FB0FCD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D14EE0B7-A1F9-4244-A5FF-F7C67150AA8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30600" yWindow="1065" windowWidth="21885" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7305" yWindow="3375" windowWidth="20175" windowHeight="13230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
   <si>
     <t>Regarding:</t>
   </si>
@@ -166,6 +166,12 @@
   </si>
   <si>
     <t>https://spdx.org/licenses/CC-BY-4.0.html</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>Germany</t>
   </si>
 </sst>
 </file>
@@ -506,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -710,6 +716,14 @@
         <v>33</v>
       </c>
     </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
